--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,119 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129574584</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bliekevare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>531097</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7168139</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129574584</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129574584</v>
       </c>
       <c r="B4" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129574584</v>
       </c>
       <c r="B4" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129574584</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129574584</v>
       </c>
       <c r="B4" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>80675723</v>
       </c>
       <c r="B2" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531058.1196622514</v>
+        <v>531058</v>
       </c>
       <c r="R2" t="n">
-        <v>7167909.142761301</v>
+        <v>7167909</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>80675722</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531237.1323066809</v>
+        <v>531237</v>
       </c>
       <c r="R3" t="n">
-        <v>7167872.811220772</v>
+        <v>7167873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +852,9 @@
           <t>2019-08-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,50 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129574584</v>
+        <v>127926840</v>
       </c>
       <c r="B4" t="n">
-        <v>56930</v>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bliekevare, Ås lm</t>
+          <t>Öster hundsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531097</v>
+        <v>531221</v>
       </c>
       <c r="R4" t="n">
-        <v>7168139</v>
+        <v>7168128</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +969,470 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Manne Frih</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Manne Frih</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129574584</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bliekevare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>531097</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7168139</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Elin Lindmark</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Via Elin Lindmark</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129574585</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bliekevare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>531242</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7168121</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129574633</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bliekevare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>531190</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7168027</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129574634</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bliekevare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>531193</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7168034</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52738-2023 artfynd.xlsx
+++ b/artfynd/A 52738-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675722</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127926840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574584</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574585</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574633</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,8 +1468,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>